--- a/2.xlsx
+++ b/2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22050" windowHeight="10755"/>
+    <workbookView windowWidth="12000" windowHeight="10755"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,39 +27,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t>北京南</t>
-  </si>
-  <si>
-    <t>上海虹桥</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="73">
+  <si>
+    <t>郑州东</t>
+  </si>
+  <si>
+    <t>石家庄</t>
+  </si>
+  <si>
+    <t>武汉</t>
+  </si>
+  <si>
+    <t>邯郸东</t>
+  </si>
+  <si>
+    <t>广州南</t>
+  </si>
+  <si>
+    <t>长沙南</t>
+  </si>
+  <si>
+    <t>天津西</t>
+  </si>
+  <si>
+    <t>济南西</t>
+  </si>
+  <si>
+    <t>徐州东</t>
+  </si>
+  <si>
+    <t>南京南</t>
+  </si>
+  <si>
+    <t>杭州东</t>
+  </si>
+  <si>
+    <t>合肥南</t>
+  </si>
+  <si>
+    <t>襄阳东</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
+    <t>南昌西</t>
+  </si>
+  <si>
+    <t>怀化南</t>
+  </si>
+  <si>
+    <t>贵阳东</t>
+  </si>
+  <si>
+    <t>秦皇岛</t>
+  </si>
+  <si>
+    <t>沈阳北</t>
+  </si>
+  <si>
+    <t>哈尔滨西</t>
+  </si>
+  <si>
+    <t>商丘</t>
+  </si>
+  <si>
+    <t>西安北</t>
   </si>
   <si>
     <t>德州东</t>
   </si>
   <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>济南西</t>
-  </si>
-  <si>
-    <t>芜湖</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>南京南</t>
-  </si>
-  <si>
-    <t>广州南</t>
-  </si>
-  <si>
-    <t>徐州东</t>
-  </si>
-  <si>
-    <t>青岛北</t>
+    <t>枣庄</t>
+  </si>
+  <si>
+    <t>宿迁</t>
+  </si>
+  <si>
+    <t>淮安东</t>
+  </si>
+  <si>
+    <t>沧州西</t>
+  </si>
+  <si>
+    <t>廊坊</t>
+  </si>
+  <si>
+    <t>蚌埠南</t>
+  </si>
+  <si>
+    <t>德阳</t>
+  </si>
+  <si>
+    <t>广元</t>
+  </si>
+  <si>
+    <t>汉中</t>
+  </si>
+  <si>
+    <t>洛阳龙门</t>
+  </si>
+  <si>
+    <t>盐城</t>
+  </si>
+  <si>
+    <t>开封北</t>
+  </si>
+  <si>
+    <t>保定东</t>
+  </si>
+  <si>
+    <t>新乡东</t>
+  </si>
+  <si>
+    <t>株洲西</t>
+  </si>
+  <si>
+    <t>耒阳西</t>
+  </si>
+  <si>
+    <t>衡阳东</t>
+  </si>
+  <si>
+    <t>安阳东</t>
+  </si>
+  <si>
+    <t>兰考南</t>
+  </si>
+  <si>
+    <t>宝鸡南</t>
+  </si>
+  <si>
+    <t>天水南</t>
+  </si>
+  <si>
+    <t>华山北</t>
+  </si>
+  <si>
+    <t>苏州北</t>
+  </si>
+  <si>
+    <t>昆山南</t>
+  </si>
+  <si>
+    <t>无锡</t>
+  </si>
+  <si>
+    <t>镇江</t>
+  </si>
+  <si>
+    <t>六安</t>
+  </si>
+  <si>
+    <t>常州北</t>
+  </si>
+  <si>
+    <t>岳阳东</t>
+  </si>
+  <si>
+    <t>贵阳北</t>
+  </si>
+  <si>
+    <t>黄山北</t>
+  </si>
+  <si>
+    <t>汉口</t>
+  </si>
+  <si>
+    <t>嘉兴南</t>
+  </si>
+  <si>
+    <t>赣州西</t>
+  </si>
+  <si>
+    <t>潍坊</t>
+  </si>
+  <si>
+    <t>韶关</t>
+  </si>
+  <si>
+    <t>菏泽东</t>
+  </si>
+  <si>
+    <t>桂林西</t>
+  </si>
+  <si>
+    <t>枣阳</t>
+  </si>
+  <si>
+    <t>宜昌北</t>
+  </si>
+  <si>
+    <t>马鞍山东</t>
+  </si>
+  <si>
+    <t>宜春</t>
+  </si>
+  <si>
+    <t>惠州南</t>
+  </si>
+  <si>
+    <t>潮汕</t>
+  </si>
+  <si>
+    <t>泰安</t>
+  </si>
+  <si>
+    <t>曲阜东</t>
+  </si>
+  <si>
+    <t>临沂北</t>
+  </si>
+  <si>
+    <t>荆门西</t>
+  </si>
+  <si>
+    <t>杭州</t>
+  </si>
+  <si>
+    <t>咸阳北</t>
   </si>
 </sst>
 </file>
@@ -72,14 +258,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,148 +714,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1001,8 +1180,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:B264"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1014,42 +1193,1994 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>26</v>
+      </c>
+      <c r="B91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>27</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>27</v>
+      </c>
+      <c r="B93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>26</v>
+      </c>
+      <c r="B94" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>29</v>
+      </c>
+      <c r="B96" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>29</v>
+      </c>
+      <c r="B101" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>31</v>
+      </c>
+      <c r="B108" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>31</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>20</v>
+      </c>
+      <c r="B116" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>35</v>
+      </c>
+      <c r="B118" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>35</v>
+      </c>
+      <c r="B119" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>35</v>
+      </c>
+      <c r="B120" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>35</v>
+      </c>
+      <c r="B121" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>35</v>
+      </c>
+      <c r="B122" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>36</v>
+      </c>
+      <c r="B123" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>36</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>36</v>
+      </c>
+      <c r="B125" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>36</v>
+      </c>
+      <c r="B126" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>37</v>
+      </c>
+      <c r="B128" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>38</v>
+      </c>
+      <c r="B130" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>38</v>
+      </c>
+      <c r="B131" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>39</v>
+      </c>
+      <c r="B132" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>41</v>
+      </c>
+      <c r="B135" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>41</v>
+      </c>
+      <c r="B136" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>41</v>
+      </c>
+      <c r="B137" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>42</v>
+      </c>
+      <c r="B138" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>42</v>
+      </c>
+      <c r="B139" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>42</v>
+      </c>
+      <c r="B140" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>32</v>
+      </c>
+      <c r="B141" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>32</v>
+      </c>
+      <c r="B142" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>43</v>
+      </c>
+      <c r="B143" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>45</v>
+      </c>
+      <c r="B145" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>45</v>
+      </c>
+      <c r="B146" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>45</v>
+      </c>
+      <c r="B147" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>45</v>
+      </c>
+      <c r="B148" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>45</v>
+      </c>
+      <c r="B149" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>45</v>
+      </c>
+      <c r="B150" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>46</v>
+      </c>
+      <c r="B151" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>46</v>
+      </c>
+      <c r="B152" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>46</v>
+      </c>
+      <c r="B153" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>46</v>
+      </c>
+      <c r="B154" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>46</v>
+      </c>
+      <c r="B155" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>47</v>
+      </c>
+      <c r="B156" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>47</v>
+      </c>
+      <c r="B157" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>47</v>
+      </c>
+      <c r="B158" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>47</v>
+      </c>
+      <c r="B159" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>48</v>
+      </c>
+      <c r="B160" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>48</v>
+      </c>
+      <c r="B161" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>48</v>
+      </c>
+      <c r="B162" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>49</v>
+      </c>
+      <c r="B163" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>49</v>
+      </c>
+      <c r="B164" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>50</v>
+      </c>
+      <c r="B165" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>10</v>
+      </c>
+      <c r="B169" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>10</v>
+      </c>
+      <c r="B170" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>10</v>
+      </c>
+      <c r="B171" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>22</v>
+      </c>
+      <c r="B172" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>22</v>
+      </c>
+      <c r="B174" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>22</v>
+      </c>
+      <c r="B175" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>22</v>
+      </c>
+      <c r="B176" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>26</v>
+      </c>
+      <c r="B177" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>26</v>
+      </c>
+      <c r="B178" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>26</v>
+      </c>
+      <c r="B179" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>26</v>
+      </c>
+      <c r="B180" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>26</v>
+      </c>
+      <c r="B181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" t="s">
+        <v>55</v>
+      </c>
+      <c r="B182" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" t="s">
+        <v>55</v>
+      </c>
+      <c r="B183" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" t="s">
+        <v>55</v>
+      </c>
+      <c r="B184" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" t="s">
+        <v>55</v>
+      </c>
+      <c r="B185" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" t="s">
+        <v>55</v>
+      </c>
+      <c r="B186" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>55</v>
+      </c>
+      <c r="B187" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>28</v>
+      </c>
+      <c r="B188" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>57</v>
+      </c>
+      <c r="B189" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>52</v>
+      </c>
+      <c r="B190" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>27</v>
+      </c>
+      <c r="B191" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>60</v>
+      </c>
+      <c r="B192" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>55</v>
+      </c>
+      <c r="B193" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>47</v>
+      </c>
+      <c r="B194" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>45</v>
+      </c>
+      <c r="B195" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>61</v>
+      </c>
+      <c r="B196" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>62</v>
+      </c>
+      <c r="B197" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>63</v>
+      </c>
+      <c r="B198" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>63</v>
+      </c>
+      <c r="B199" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>63</v>
+      </c>
+      <c r="B200" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>63</v>
+      </c>
+      <c r="B201" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>63</v>
+      </c>
+      <c r="B202" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>63</v>
+      </c>
+      <c r="B203" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>63</v>
+      </c>
+      <c r="B204" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>63</v>
+      </c>
+      <c r="B205" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>63</v>
+      </c>
+      <c r="B206" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>53</v>
+      </c>
+      <c r="B207" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>52</v>
+      </c>
+      <c r="B208" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" t="s">
+        <v>5</v>
+      </c>
+      <c r="B209" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" t="s">
+        <v>54</v>
+      </c>
+      <c r="B210" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" t="s">
+        <v>70</v>
+      </c>
+      <c r="B211" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" t="s">
+        <v>70</v>
+      </c>
+      <c r="B212" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" t="s">
+        <v>70</v>
+      </c>
+      <c r="B213" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" t="s">
+        <v>70</v>
+      </c>
+      <c r="B214" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" t="s">
+        <v>70</v>
+      </c>
+      <c r="B215" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" t="s">
+        <v>70</v>
+      </c>
+      <c r="B216" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" t="s">
+        <v>70</v>
+      </c>
+      <c r="B217" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" t="s">
+        <v>70</v>
+      </c>
+      <c r="B218" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" t="s">
+        <v>70</v>
+      </c>
+      <c r="B219" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" t="s">
+        <v>12</v>
+      </c>
+      <c r="B220" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" t="s">
+        <v>12</v>
+      </c>
+      <c r="B221" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" t="s">
+        <v>12</v>
+      </c>
+      <c r="B223" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>12</v>
+      </c>
+      <c r="B226" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>72</v>
+      </c>
+      <c r="B229" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>72</v>
+      </c>
+      <c r="B230" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>72</v>
+      </c>
+      <c r="B231" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>72</v>
+      </c>
+      <c r="B232" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>72</v>
+      </c>
+      <c r="B233" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>72</v>
+      </c>
+      <c r="B234" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>72</v>
+      </c>
+      <c r="B235" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>72</v>
+      </c>
+      <c r="B236" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>72</v>
+      </c>
+      <c r="B237" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>29</v>
+      </c>
+      <c r="B238" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>29</v>
+      </c>
+      <c r="B239" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>29</v>
+      </c>
+      <c r="B240" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>29</v>
+      </c>
+      <c r="B241" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>29</v>
+      </c>
+      <c r="B242" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>29</v>
+      </c>
+      <c r="B243" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>29</v>
+      </c>
+      <c r="B244" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>31</v>
+      </c>
+      <c r="B245" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>31</v>
+      </c>
+      <c r="B246" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>31</v>
+      </c>
+      <c r="B247" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>31</v>
+      </c>
+      <c r="B248" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>31</v>
+      </c>
+      <c r="B249" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>31</v>
+      </c>
+      <c r="B250" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" t="s">
+        <v>31</v>
+      </c>
+      <c r="B251" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>23</v>
+      </c>
+      <c r="B252" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>24</v>
+      </c>
+      <c r="B253" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>25</v>
+      </c>
+      <c r="B254" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>26</v>
+      </c>
+      <c r="B255" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" t="s">
+        <v>27</v>
+      </c>
+      <c r="B256" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" t="s">
+        <v>26</v>
+      </c>
+      <c r="B257" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" t="s">
+        <v>28</v>
+      </c>
+      <c r="B258" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" t="s">
+        <v>42</v>
+      </c>
+      <c r="B259" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" t="s">
+        <v>42</v>
+      </c>
+      <c r="B260" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" t="s">
+        <v>42</v>
+      </c>
+      <c r="B261" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" t="s">
+        <v>42</v>
+      </c>
+      <c r="B262" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" t="s">
+        <v>42</v>
+      </c>
+      <c r="B263" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" t="s">
+        <v>42</v>
+      </c>
+      <c r="B264" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
